--- a/medford_telezhki_dlya_uzi.xlsx
+++ b/medford_telezhki_dlya_uzi.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Тележки для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray — всего 4 позиций.</t>
+          <t>Тележки для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_telezhki_dlya_uzi.xlsx
+++ b/medford_telezhki_dlya_uzi.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать тележки для УЗИ для клиники?</t>
+          <t>Как понять, подойдёт ли тележка к моему сканеру?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Фирменные тележки привязаны к конкретной серии сканера по размерам и креплениям. В каталоге Edan MT-808 рассчитана на Acclarix AX3, Mindray UMT-200 — на M5/M7, MT3 — на MX7 и MX8 Exp, UMT-500 — на M9. Сначала уточняют точную модель аппарата, затем сверяют её с назначением тележки по документации до покупки.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем фирменная тележка лучше универсальной?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>У фирменной тележки крепления и посадочное место подогнаны под конкретную серию сканера, что обеспечивает устойчивость и аккуратный монтаж без переходников. Универсальные модели подходят под разные аппараты, но требуют проверки совместимости размеров и креплений. При наличии штатной тележки под модель обычно выбирают её ради надёжной фиксации сканера.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Сколько держателей для датчиков нужно?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Edan, Mindray. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Число держателей подбирают под количество датчиков, с которыми работает сканер, чтобы все преобразователи хранились безопасно и под рукой. Тележки обычно комплектуют держателями на несколько датчиков и лотком для геля. Точный состав держателей у конкретной модели сверяют по спецификации у поставщика перед приобретением.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Регулируется ли тележка по высоте?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Часть тележек имеет регулировку по высоте и дополнительные корзины для принадлежностей, что делает рабочее место эргономичнее. Наличие регулировки зависит от конкретной модели. Нужный набор функций определяют по характеру работы отделения и уточняют по документации выбранной тележки, не перенося характеристики других моделей.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Насколько устойчива тележка при перемещении?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Мобильность обеспечивают колёса, а устойчивость во время исследования — стопоры-тормоза, фиксирующие тележку на месте. Поскольку на ней размещён сканер, качество стопорного механизма и общая устойчивость важны. Тип колёс и наличие фиксаторов сверяют по спецификации; для частых перемещений между кабинетами это один из ключевых параметров.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Из чего сделан каркас тележки?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Каркас тележек для УЗИ обычно металлический, с элементами из пластика, и рассчитан на регулярное перемещение с закреплённым сканером. Конкретное исполнение и материалы уточняют по документации выбранной модели. Прочность каркаса влияет на устойчивость аппарата и срок службы тележки при интенсивной эксплуатации в отделении.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>telezhki_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли отдельно проверять оформление тележки?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Тележка — принадлежность к ультразвуковому сканеру, поэтому перед приобретением сверяют комплектацию (адаптер питания, кабель, корзины) и условия поставки у поставщика, а также требования к её оформлению в комплекте с аппаратом. Это уточняют заранее, чтобы тележка соответствовала конкретной модели сканера и её документации.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>telezhki_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Тележки для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Edan, Mindray.</t>
+          <t>Тележки для УЗИ предназначены для размещения и перемещения портативного ультразвукового сканера по отделению с превращением его в мобильное рабочее место. В каталоге представлены фирменные тележки Edan и Mindray, каждая из которых рассчитана на конкретную серию сканера: Edan MT-808 — под Acclarix AX3, Mindray UMT-200 — под модели M5/M7, MT3 — под MX7 и MX8 Exp, UMT-500 — под M9. Тележки оснащаются полками, держателями для датчиков и стопорными колёсами для фиксации во время исследования.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое тележки для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3256,7 +3332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3582,12 +3658,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите модель сканера</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается тележки для УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Совместимость тележки первична, поэтому начинают с точной модели портативного сканера. Фирменные тележки каталога привязаны к сериям: Edan MT-808 — к Acclarix AX3, Mindray UMT-200 — к M5/M7, MT3 — к MX7, MX7 Exp и MX8 Exp, UMT-500 — к M9. Тележку подбирают под аппарат, а не наоборот.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3627,12 +3703,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите фирменную или универсальную</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Фирменная тележка рассчитана на конкретную серию: крепления и посадочное место подогнаны под аппарат, что обеспечивает устойчивость и аккуратный монтаж. Универсальные модели подходят под разные сканеры, но требуют проверки размеров и креплений. Если фирменная тележка под вашу модель есть, обычно выбирают её; универсальную берут при отсутствии штатной.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3672,12 +3748,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте держатели для датчиков</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Тележки оснащаются держателями для датчиков — обычно на несколько преобразователей — и лотком для геля. Число держателей должно соответствовать количеству датчиков, с которыми работает сканер, чтобы они хранились безопасно и под рукой. Конкретную комплектацию держателей сверяют по спецификации выбранной модели тележки у поставщика.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3717,12 +3793,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените регулировку и хранение</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Edan, Mindray.</t>
+          <t>Часть тележек регулируется по высоте и имеет корзины для принадлежностей и держатель для геля, что делает рабочее место эргономичнее. Наличие регулировки и дополнительных отсеков зависит от модели. Нужный набор функций определяют по характеру работы отделения и уточняют по документации конкретной тележки перед приобретением.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3762,12 +3838,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте колёса и фиксацию</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Мобильность обеспечивают колёса, а безопасность во время исследования — надёжные стопоры-тормоза, фиксирующие тележку на месте. Устойчивость и качество стопорного механизма важны, поскольку на тележке размещён дорогой сканер. Тип колёс и наличие фиксаторов сверяют по спецификации; для частых перемещений между кабинетами это ключевой параметр.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3807,12 +3883,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните каркас и поставку</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Каркас тележек обычно металлический с элементами из пластика; конкретное исполнение уточняют по документации модели. Перед приобретением сверяют комплектацию (адаптер питания, кабель, корзины) и условия поставки у поставщика. Поскольку тележка — принадлежность к медицинскому изделию, уточняют и требования к её оформлению в комплекте со сканером.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3862,7 +3938,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Тележки для УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Edan, Mindray. При выборе обращают внимание на страна производства, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Тележку выбирают не отдельно, а под конкретный сканер — это её главный параметр. Фирменные модели рассчитаны на свою серию: Mindray UMT-200 под M5 и M7, MT3 под MX7 и MX8 Exp, UMT-500 под M9, Edan MT-808 под Acclarix AX3. Крепления и посадочное место у них подогнаны под аппарат, поэтому универсальную тележку я беру только когда фирменной под модель нет. Дальше смотрю на число держателей датчиков и надёжность стопоров.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4146,13 +4222,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое тележки для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Тележки для УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Edan, Mindray. Подберём вариант под задачи вашего отделения.</t>
+          <t>Тележка для УЗИ превращает портативный сканер в мобильное рабочее место: она несёт аппарат, датчики и принадлежности и фиксируется на месте стопорными колёсами. Главный критерий выбора — совместимость с конкретной моделью сканера, так как крепления и размеры фирменных тележек привязаны к серии аппарата. В каталоге это Edan MT-808 (под Acclarix AX3) и Mindray UMT-200, MT3, UMT-500 (под M5/M7, MX7 и MX8 Exp, M9). Дальше оценивают число держателей для датчиков, регулировку по высоте, наличие корзин для принадлежностей и надёжность стопорного механизма.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4189,13 +4265,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое тележка для УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Тележка для УЗИ — мобильная стойка для размещения портативного ультразвукового сканера, датчиков и принадлежностей. Она превращает переносной аппарат в полноценное передвижное рабочее место, оснащается полками, держателями для датчиков, лотком для геля и стопорными колёсами для фиксации во время исследования.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4232,13 +4308,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Совместимость со сканером</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Главный критерий выбора тележки — совместимость с конкретной моделью сканера. Фирменные тележки каталога привязаны к сериям: Edan MT-808 — к Acclarix AX3, Mindray UMT-200 — к M5/M7, MT3 — к MX7 и MX8 Exp, UMT-500 — к M9. Крепления и размеры подогнаны под аппарат, поэтому тележку подбирают под сканер.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4275,13 +4351,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Как выбрать тележку</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>После определения модели сканера выбирают между фирменным и универсальным исполнением, проверяют число держателей для датчиков, наличие регулировки по высоте и корзин для принадлежностей. Отдельно оценивают колёса и надёжность стопоров-тормозов, поскольку на тележке размещён дорогой аппарат и важна устойчивость при перемещении.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4298,6 +4374,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Комплектация и эксплуатация</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Тележки обычно имеют металлический каркас с пластиковыми элементами, держатели для нескольких датчиков, корзины и держатель для геля. Перед приобретением сверяют комплектацию, условия поставки и совместимость с конкретной моделью сканера. Надёжная фиксация колёс и устойчивость каркаса обеспечивают безопасное перемещение аппарата по отделению.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>telezhki_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
